--- a/school_2/vor_spartac_2_floors.xlsx
+++ b/school_2/vor_spartac_2_floors.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="7 с" sheetId="1" r:id="rId1"/>
+    <sheet name="Спец 7 с" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -165,6 +170,8 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -484,7 +491,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,15 +623,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,6 +642,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,6 +667,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -705,7 +718,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -740,7 +753,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -949,18 +962,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K14"/>
+  <dimension ref="B1:J14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
     <col min="3" max="3" width="54.85546875" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="40" t="s">
         <v>33</v>
@@ -969,9 +982,8 @@
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
       <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-    </row>
-    <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>0</v>
       </c>
@@ -988,9 +1000,8 @@
         <v>4</v>
       </c>
       <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="22">
         <v>1</v>
       </c>
@@ -1007,15 +1018,14 @@
         <v>627.35</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="J4" s="25">
+      <c r="I4" s="25">
         <v>1</v>
       </c>
-      <c r="K4" s="26">
+      <c r="J4" s="26">
         <v>3730.5</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="6">
         <v>1.1000000000000001</v>
       </c>
@@ -1028,21 +1038,20 @@
       <c r="E5" s="10">
         <v>8</v>
       </c>
-      <c r="F5" s="9">
-        <f>F$4*E5</f>
-        <v>5018.8</v>
+      <c r="F5" s="52">
+        <f>ROUNDUP(F$4*E5, 0)</f>
+        <v>5019</v>
       </c>
       <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="J5" s="8">
+      <c r="I5" s="8">
         <v>8</v>
       </c>
-      <c r="K5" s="9">
-        <f>K$4*J5</f>
+      <c r="J5" s="9">
+        <f>J$4*I5</f>
         <v>29844</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="41" t="s">
         <v>8</v>
       </c>
@@ -1060,16 +1069,15 @@
         <v>40.777750000000005</v>
       </c>
       <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="J6" s="8">
+      <c r="I6" s="8">
         <v>1E-3</v>
       </c>
-      <c r="K6" s="36">
-        <f>K4*$E6*0.065*1000</f>
+      <c r="J6" s="36">
+        <f>J4*$E6*0.065*1000</f>
         <v>242.48250000000002</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="41" t="s">
         <v>9</v>
       </c>
@@ -1087,16 +1095,15 @@
         <v>690.08500000000004</v>
       </c>
       <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="J7" s="8">
+      <c r="I7" s="8">
         <v>1.1000000000000001</v>
       </c>
-      <c r="K7" s="9">
-        <f>K$4*J7</f>
+      <c r="J7" s="9">
+        <f>J$4*I7</f>
         <v>4103.55</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
         <v>29</v>
       </c>
@@ -1114,16 +1121,15 @@
         <v>13048.880000000001</v>
       </c>
       <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="J8" s="8">
+      <c r="I8" s="8">
         <v>0.32</v>
       </c>
-      <c r="K8" s="36">
-        <f>K$4*J$8*0.065*1000</f>
+      <c r="J8" s="36">
+        <f>J$4*I$8*0.065*1000</f>
         <v>77594.400000000009</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="41" t="s">
         <v>30</v>
       </c>
@@ -1141,16 +1147,15 @@
         <v>40.777750000000012</v>
       </c>
       <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="J9" s="8">
+      <c r="I9" s="8">
         <v>1E-3</v>
       </c>
-      <c r="K9" s="36">
-        <f>K4*$J9*0.065*1000</f>
+      <c r="J9" s="36">
+        <f>J4*$I9*0.065*1000</f>
         <v>242.48250000000002</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>31</v>
       </c>
@@ -1167,15 +1172,14 @@
         <v>269.12</v>
       </c>
       <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="J10" s="8">
+      <c r="I10" s="8">
         <v>1</v>
       </c>
-      <c r="K10" s="9">
+      <c r="J10" s="9">
         <v>1876</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>32</v>
       </c>
@@ -1193,31 +1197,27 @@
         <v>125.47000000000001</v>
       </c>
       <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="J11" s="13">
+      <c r="I11" s="13">
         <v>0.2</v>
       </c>
-      <c r="K11" s="9">
-        <f>$K$4*J11</f>
+      <c r="J11" s="9">
+        <f>$J$4*I11</f>
         <v>746.1</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="31"/>
       <c r="C12" s="32"/>
       <c r="D12" s="33"/>
       <c r="E12" s="34"/>
       <c r="F12" s="33"/>
       <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1236,11 +1236,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -1320,26 +1320,26 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49">
+      <c r="A9" s="46">
         <v>7</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="48">
         <v>93.34</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53" t="s">
+      <c r="A10" s="49"/>
+      <c r="B10" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="51">
         <f>SUM(C3:C9)</f>
         <v>627.35</v>
       </c>
-      <c r="E10" s="48"/>
+      <c r="E10" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/school_2/vor_spartac_2_floors.xlsx
+++ b/school_2/vor_spartac_2_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="7 с" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -89,9 +89,6 @@
     <t>Фиксатор арматуры Звездочка_/15/4-16</t>
   </si>
   <si>
-    <t>Фиброволокно_/7-12мм</t>
-  </si>
-  <si>
     <t>Сетка эл/св_/100*100*5</t>
   </si>
   <si>
@@ -101,12 +98,6 @@
     <t>Грунтовка универсальный ЛАСТИМИН_ / УНКОНТ ЛЮКС LP51 А</t>
   </si>
   <si>
-    <t>Цемент_М500</t>
-  </si>
-  <si>
-    <t>Песок_ мытый</t>
-  </si>
-  <si>
     <t>шт</t>
   </si>
   <si>
@@ -116,16 +107,16 @@
     <t>1.5</t>
   </si>
   <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
     <t>Ведомость работ и используемых материалов</t>
   </si>
   <si>
     <t>2.063</t>
+  </si>
+  <si>
+    <t>Смесь цементно-песчаная сухая_/М150</t>
+  </si>
+  <si>
+    <t>м2</t>
   </si>
 </sst>
 </file>
@@ -189,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -237,49 +228,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -491,7 +439,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -502,85 +450,67 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -595,65 +525,52 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -962,262 +879,196 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J14"/>
+  <dimension ref="B1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
     <col min="3" max="3" width="54.85546875" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
-      <c r="C2" s="40" t="s">
-        <v>33</v>
+      <c r="C2" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
+    </row>
+    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="37"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="22">
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="16">
         <v>1</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="19">
         <v>1</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="20">
         <v>627.35</v>
       </c>
-      <c r="G4" s="33"/>
-      <c r="I4" s="25">
+      <c r="H4" s="19">
         <v>1</v>
       </c>
-      <c r="J4" s="26">
+      <c r="I4" s="20">
         <v>3730.5</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="6">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="C5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="33">
+        <f>F$4*E5</f>
+        <v>125.47000000000001</v>
+      </c>
+      <c r="H5" s="6">
         <v>8</v>
       </c>
-      <c r="F5" s="52">
-        <f>ROUNDUP(F$4*E5, 0)</f>
-        <v>5019</v>
-      </c>
-      <c r="G5" s="33"/>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
+        <f>I$4*H5</f>
+        <v>29844</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="9">
-        <f>J$4*I5</f>
-        <v>29844</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="33">
+        <v>269.12</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="I6" s="30">
+        <f>I4*$E6*0.065*1000</f>
+        <v>242482.50000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1E-3</v>
-      </c>
-      <c r="F6" s="42">
-        <f>F4*$E6*65</f>
-        <v>40.777750000000005</v>
-      </c>
-      <c r="G6" s="38"/>
-      <c r="I6" s="8">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="36">
-        <f>J4*$E6*0.065*1000</f>
-        <v>242.48250000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="8">
+      <c r="D7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="33">
         <f>F$4*E7</f>
         <v>690.08500000000004</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="I7" s="8">
+      <c r="H7" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J7" s="9">
-        <f>J$4*I7</f>
+      <c r="I7" s="7">
+        <f>I$4*H7</f>
         <v>4103.55</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="21" t="s">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="F8" s="33">
+        <f>F$4*E$8*0.065*1000</f>
+        <v>73399.95</v>
+      </c>
+      <c r="H8" s="6">
         <v>0.32</v>
       </c>
-      <c r="F8" s="42">
-        <f>F$4*E$8*0.065*1000</f>
-        <v>13048.880000000001</v>
-      </c>
-      <c r="G8" s="38"/>
-      <c r="I8" s="8">
-        <v>0.32</v>
-      </c>
-      <c r="J8" s="36">
-        <f>J$4*I$8*0.065*1000</f>
+      <c r="I8" s="30">
+        <f>I$4*H$8*0.065*1000</f>
         <v>77594.400000000009</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="21" t="s">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="C9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>8</v>
+      </c>
+      <c r="F9" s="41">
+        <f>ROUNDUP(F$4*E9, 0)</f>
+        <v>5019</v>
+      </c>
+      <c r="H9" s="6">
         <v>1E-3</v>
       </c>
-      <c r="F9" s="42">
-        <f>F4*$E9*0.065*1000</f>
-        <v>40.777750000000012</v>
-      </c>
-      <c r="G9" s="38"/>
-      <c r="I9" s="8">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="36">
-        <f>J4*$I9*0.065*1000</f>
+      <c r="I9" s="30">
+        <f>I4*$H9*0.065*1000</f>
         <v>242.48250000000002</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9">
-        <v>269.12</v>
-      </c>
-      <c r="G10" s="33"/>
-      <c r="I10" s="8">
-        <v>1</v>
-      </c>
-      <c r="J10" s="9">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="F11" s="9">
-        <f>$F$4*E11</f>
-        <v>125.47000000000001</v>
-      </c>
-      <c r="G11" s="33"/>
-      <c r="I11" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="J11" s="9">
-        <f>$J$4*I11</f>
-        <v>746.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="31"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G13" s="39"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G14" s="39"/>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1230,116 +1081,116 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="18"/>
-    <col min="2" max="2" width="13.7109375" style="18" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="18"/>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="13.7109375" style="12" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="55"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="44"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="7">
         <v>35.82</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="7">
         <v>35.08</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>169.95</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>217.09</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="16">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="7">
         <v>10.88</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="16">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <v>65.19</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="46">
+      <c r="A9" s="35">
         <v>7</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="37">
         <v>93.34</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="40">
         <f>SUM(C3:C9)</f>
         <v>627.35</v>
       </c>
-      <c r="E10" s="45"/>
+      <c r="E10" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/school_2/vor_spartac_2_floors.xlsx
+++ b/school_2/vor_spartac_2_floors.xlsx
@@ -9,19 +9,38 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="858" firstSheet="5" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="7 с" sheetId="1" r:id="rId1"/>
-    <sheet name="Спец 7 с" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="спец7с" sheetId="2" r:id="rId2"/>
+    <sheet name="Вор" sheetId="3" r:id="rId3"/>
+    <sheet name="спец6с" sheetId="4" r:id="rId4"/>
+    <sheet name="спец5с" sheetId="5" r:id="rId5"/>
+    <sheet name="спец4с" sheetId="6" r:id="rId6"/>
+    <sheet name="спец4с (2)" sheetId="7" r:id="rId7"/>
+    <sheet name="Вор3э" sheetId="16" r:id="rId8"/>
+    <sheet name="7сэ3" sheetId="9" r:id="rId9"/>
+    <sheet name="6с3э" sheetId="10" r:id="rId10"/>
+    <sheet name="4с3э" sheetId="12" r:id="rId11"/>
+    <sheet name="3с3э" sheetId="13" r:id="rId12"/>
+    <sheet name="2с3э" sheetId="14" r:id="rId13"/>
+    <sheet name="1с3" sheetId="15" r:id="rId14"/>
+    <sheet name="спец" sheetId="8" r:id="rId15"/>
+    <sheet name="1с" sheetId="18" r:id="rId16"/>
+    <sheet name="2с" sheetId="19" r:id="rId17"/>
+    <sheet name="3с" sheetId="20" r:id="rId18"/>
+    <sheet name="4_5с" sheetId="22" r:id="rId19"/>
+    <sheet name="6с" sheetId="23" r:id="rId20"/>
+    <sheet name="Вор2э" sheetId="24" r:id="rId21"/>
+    <sheet name="Лист1" sheetId="17" r:id="rId22"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="151">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -117,6 +136,368 @@
   </si>
   <si>
     <t>м2</t>
+  </si>
+  <si>
+    <t>3.038</t>
+  </si>
+  <si>
+    <t>3.039</t>
+  </si>
+  <si>
+    <t>3.040</t>
+  </si>
+  <si>
+    <t>3.041</t>
+  </si>
+  <si>
+    <t>3.042</t>
+  </si>
+  <si>
+    <t>3.043</t>
+  </si>
+  <si>
+    <t>3.044</t>
+  </si>
+  <si>
+    <t>3.045</t>
+  </si>
+  <si>
+    <t>3.046</t>
+  </si>
+  <si>
+    <t>2.048</t>
+  </si>
+  <si>
+    <t>2.049</t>
+  </si>
+  <si>
+    <t>2.050</t>
+  </si>
+  <si>
+    <t>2.051</t>
+  </si>
+  <si>
+    <t>2.052</t>
+  </si>
+  <si>
+    <t>2.053</t>
+  </si>
+  <si>
+    <t>2.054-2.069</t>
+  </si>
+  <si>
+    <t>2.055</t>
+  </si>
+  <si>
+    <t>2.056</t>
+  </si>
+  <si>
+    <t>Объем. м²</t>
+  </si>
+  <si>
+    <t>2.045</t>
+  </si>
+  <si>
+    <t>2.046</t>
+  </si>
+  <si>
+    <t>2.047</t>
+  </si>
+  <si>
+    <t>2.036</t>
+  </si>
+  <si>
+    <t>2.038</t>
+  </si>
+  <si>
+    <t>2.039</t>
+  </si>
+  <si>
+    <t>2.040</t>
+  </si>
+  <si>
+    <t>2.041</t>
+  </si>
+  <si>
+    <t>2.042</t>
+  </si>
+  <si>
+    <t>2.043</t>
+  </si>
+  <si>
+    <t>2.071</t>
+  </si>
+  <si>
+    <t>3.001</t>
+  </si>
+  <si>
+    <t>3.002</t>
+  </si>
+  <si>
+    <t>3.003</t>
+  </si>
+  <si>
+    <t>3.004</t>
+  </si>
+  <si>
+    <t>3.005</t>
+  </si>
+  <si>
+    <t>3.006</t>
+  </si>
+  <si>
+    <t>3.007</t>
+  </si>
+  <si>
+    <t>3.008</t>
+  </si>
+  <si>
+    <t>3.009</t>
+  </si>
+  <si>
+    <t>3.010</t>
+  </si>
+  <si>
+    <t>3.011</t>
+  </si>
+  <si>
+    <t>3.012</t>
+  </si>
+  <si>
+    <t>3.013</t>
+  </si>
+  <si>
+    <t>3.014</t>
+  </si>
+  <si>
+    <t>3.015</t>
+  </si>
+  <si>
+    <t>3.016</t>
+  </si>
+  <si>
+    <t>3.017</t>
+  </si>
+  <si>
+    <t>3.018</t>
+  </si>
+  <si>
+    <t>3.019</t>
+  </si>
+  <si>
+    <t>3.020</t>
+  </si>
+  <si>
+    <t>3.021</t>
+  </si>
+  <si>
+    <t>3.022</t>
+  </si>
+  <si>
+    <t>3.023</t>
+  </si>
+  <si>
+    <t>3.024</t>
+  </si>
+  <si>
+    <t>3.025</t>
+  </si>
+  <si>
+    <t>3.026</t>
+  </si>
+  <si>
+    <t>3.027</t>
+  </si>
+  <si>
+    <t>3.028</t>
+  </si>
+  <si>
+    <t>3.029</t>
+  </si>
+  <si>
+    <t>3.030</t>
+  </si>
+  <si>
+    <t>3.031</t>
+  </si>
+  <si>
+    <t>3.032</t>
+  </si>
+  <si>
+    <t>3.033</t>
+  </si>
+  <si>
+    <t>3.034</t>
+  </si>
+  <si>
+    <t>3.035</t>
+  </si>
+  <si>
+    <t>3.036</t>
+  </si>
+  <si>
+    <t>3.037</t>
+  </si>
+  <si>
+    <t>3.047</t>
+  </si>
+  <si>
+    <t>3.048</t>
+  </si>
+  <si>
+    <t>3.049</t>
+  </si>
+  <si>
+    <t>3.050</t>
+  </si>
+  <si>
+    <t>3.051</t>
+  </si>
+  <si>
+    <t>3.052</t>
+  </si>
+  <si>
+    <t>3.053</t>
+  </si>
+  <si>
+    <t>3.054</t>
+  </si>
+  <si>
+    <t>3.055</t>
+  </si>
+  <si>
+    <t>3.057</t>
+  </si>
+  <si>
+    <t>3.058</t>
+  </si>
+  <si>
+    <t>3.059</t>
+  </si>
+  <si>
+    <t>3.060</t>
+  </si>
+  <si>
+    <t>3.061</t>
+  </si>
+  <si>
+    <t>3.062</t>
+  </si>
+  <si>
+    <t>3.063</t>
+  </si>
+  <si>
+    <t>3.064</t>
+  </si>
+  <si>
+    <t>3.065</t>
+  </si>
+  <si>
+    <t>3.066</t>
+  </si>
+  <si>
+    <t>3.067</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (7 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (6 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (5, 4 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (3 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (2 секция)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (1 секция)</t>
+  </si>
+  <si>
+    <t>а</t>
+  </si>
+  <si>
+    <t>ТИП 14</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой от 61мм до 80мм
+3 этаж. Стяжка толщиной 65 мм. Тип: П-12, П-13, П-15, П-16.</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой от 41 мм до 60 мм
+3 этаж. Стяжка толщиной 60 мм. Тип: П-14</t>
+  </si>
+  <si>
+    <t>2.070</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (4, 5 секция)</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой от 61мм до 80мм
+2 этаж. Стяжка толщиной 65 мм. Тип: П-12, П-13, П-15, П-16.</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой от 41 мм до 60 мм
+2 этаж. Стяжка толщиной 60 мм. П-14</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Устройство стяжки СКБ / армированная сеткой от 41 мм до 60 мм
+2 этаж. Стяжка толщиной 50 мм. Тип: П18, П-18.1</t>
+  </si>
+  <si>
+    <t>2.057</t>
+  </si>
+  <si>
+    <t>ТИП 18</t>
+  </si>
+  <si>
+    <t>ТИП 18.1</t>
+  </si>
+  <si>
+    <t>2.065</t>
+  </si>
+  <si>
+    <t>2.020</t>
   </si>
 </sst>
 </file>
@@ -127,7 +508,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,16 +552,37 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -433,13 +835,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,6 +1056,74 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -572,6 +1132,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -879,7 +1448,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I10"/>
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="B1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.5703125" customWidth="1"/>
@@ -1070,14 +1642,2709 @@
       <c r="E10" s="28"/>
       <c r="F10" s="27"/>
     </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <f>F4/F6</f>
+        <v>2.3311162306777646</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="30">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="30">
+        <v>115.30000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="30">
+        <v>195.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="30">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="30">
+        <v>118.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="30">
+        <v>164.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="30">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="30">
+        <v>21.400000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="30">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="30">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="30">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="43">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="56">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="43">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="55">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="B16" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="57">
+        <f>SUM(C3:C15)</f>
+        <v>755.20000000000016</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="30">
+        <v>88.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="30">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="30">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="30">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="30">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="30">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="30">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="30">
+        <v>62.199999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="55">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="55">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="55">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="43">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="55">
+        <v>99.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="40">
+        <f>SUM(C3:C14)</f>
+        <v>563.19999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="30">
+        <v>319.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="7">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="30">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="30">
+        <v>73.800000000000011</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="30">
+        <v>187.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="30">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="30">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="30">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="56">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="55">
+        <v>71.599999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="40">
+        <f>SUM(C3:C12)</f>
+        <v>805.88000000000011</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="30">
+        <v>101.39999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="30">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="30">
+        <v>235.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="30">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="30">
+        <v>62.300000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="30">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="30">
+        <v>18.220000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="30">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="30">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="30">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="55">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
+      <c r="B14" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="57">
+        <f>SUM(C3:C13)</f>
+        <v>623.51999999999987</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="41">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="30">
+        <v>62.599999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="30">
+        <v>83.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="30">
+        <v>244.20000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="30">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="30">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="30">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="30">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38"/>
+      <c r="B11" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="59">
+        <f>SUM(C3:C10)</f>
+        <v>520.30000000000007</v>
+      </c>
+    </row>
+    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:D115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="7">
+        <v>80.3</v>
+      </c>
+      <c r="D2" s="47">
+        <f ca="1">C2-RANDBETWEEN(0, 10)/10</f>
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="43"/>
+      <c r="B3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="7">
+        <v>63.3</v>
+      </c>
+      <c r="D3" s="47">
+        <f t="shared" ref="D3:D66" ca="1" si="0">C3-RANDBETWEEN(0, 10)/10</f>
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="43"/>
+      <c r="B4" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="7">
+        <v>84.7</v>
+      </c>
+      <c r="D4" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>84.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="43"/>
+      <c r="B5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="7">
+        <v>244.9</v>
+      </c>
+      <c r="D5" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D6" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>18.299999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="43"/>
+      <c r="B7" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="49">
+        <v>10</v>
+      </c>
+      <c r="D7" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="43"/>
+      <c r="B8" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="7">
+        <v>9.1</v>
+      </c>
+      <c r="D8" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="B9" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="D9" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="D10" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="B11" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="7">
+        <v>103.1</v>
+      </c>
+      <c r="D11" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>102.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="43"/>
+      <c r="B12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="7">
+        <v>89.8</v>
+      </c>
+      <c r="D12" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="43"/>
+      <c r="B13" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="7">
+        <v>235.7</v>
+      </c>
+      <c r="D13" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>234.79999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="B14" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="7">
+        <v>63</v>
+      </c>
+      <c r="D14" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="43"/>
+      <c r="B15" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="7">
+        <v>63.6</v>
+      </c>
+      <c r="D15" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="B16" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="7">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D16" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
+      <c r="B17" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="49">
+        <v>10</v>
+      </c>
+      <c r="D17" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="43"/>
+      <c r="B18" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="D18" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="43"/>
+      <c r="B19" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="D19" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="43"/>
+      <c r="B20" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="7">
+        <v>320.39999999999998</v>
+      </c>
+      <c r="D20" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>319.79999999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="43"/>
+      <c r="B21" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="D21" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="43"/>
+      <c r="B22" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="7">
+        <v>24.7</v>
+      </c>
+      <c r="D22" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="43"/>
+      <c r="B23" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="7">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="D23" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="43"/>
+      <c r="B24" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="7">
+        <v>188.6</v>
+      </c>
+      <c r="D24" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>188.29999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="43"/>
+      <c r="B25" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="49">
+        <v>10</v>
+      </c>
+      <c r="D25" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="43"/>
+      <c r="B26" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="D26" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="43"/>
+      <c r="B27" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="D27" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="43"/>
+      <c r="B28" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="7">
+        <v>90.2</v>
+      </c>
+      <c r="D28" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="43"/>
+      <c r="B29" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="7">
+        <v>63.5</v>
+      </c>
+      <c r="D29" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="43"/>
+      <c r="B30" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D30" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="43"/>
+      <c r="B31" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="7">
+        <v>63.9</v>
+      </c>
+      <c r="D31" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>63.699999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="43"/>
+      <c r="B32" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="7">
+        <v>64.2</v>
+      </c>
+      <c r="D32" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="43"/>
+      <c r="B33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="7">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="D33" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>63.399999999999991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="43"/>
+      <c r="B34" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="7">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D34" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>8.2999999999999989</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="43"/>
+      <c r="B35" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="49">
+        <v>10</v>
+      </c>
+      <c r="D35" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="43"/>
+      <c r="B36" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="7">
+        <v>63.3</v>
+      </c>
+      <c r="D36" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="43"/>
+      <c r="B37" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="7">
+        <v>62.6</v>
+      </c>
+      <c r="D37" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="43"/>
+      <c r="B38" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="7">
+        <v>116.4</v>
+      </c>
+      <c r="D38" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>115.60000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="43"/>
+      <c r="B39" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="7">
+        <v>197.4</v>
+      </c>
+      <c r="D39" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>197.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="43"/>
+      <c r="B40" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="7">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D40" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="43"/>
+      <c r="B41" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="7">
+        <v>120.7</v>
+      </c>
+      <c r="D41" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>120.10000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="43"/>
+      <c r="B42" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="7">
+        <v>165.8</v>
+      </c>
+      <c r="D42" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>165.20000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="43"/>
+      <c r="B43" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="7">
+        <v>22.2</v>
+      </c>
+      <c r="D43" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>22.099999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="43"/>
+      <c r="B44" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="7">
+        <v>22.1</v>
+      </c>
+      <c r="D44" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="43"/>
+      <c r="B45" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D45" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.1000000000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="43"/>
+      <c r="B46" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="7">
+        <v>5.6</v>
+      </c>
+      <c r="D46" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="43"/>
+      <c r="B47" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="7">
+        <v>9.1</v>
+      </c>
+      <c r="D47" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="43"/>
+      <c r="B48" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="50">
+        <v>10</v>
+      </c>
+      <c r="D48" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="43"/>
+      <c r="B49" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="37">
+        <v>94</v>
+      </c>
+      <c r="D49" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>93.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="43"/>
+      <c r="B50" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="37">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="D50" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>40.199999999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="43"/>
+      <c r="B51" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="5">
+        <v>156.4</v>
+      </c>
+      <c r="D51" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>155.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="43"/>
+      <c r="B52" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="5">
+        <v>198.1</v>
+      </c>
+      <c r="D52" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>197.29999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="43"/>
+      <c r="B53" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="51">
+        <v>10</v>
+      </c>
+      <c r="D53" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="43"/>
+      <c r="B54" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="5">
+        <v>200.9</v>
+      </c>
+      <c r="D54" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>200.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="43"/>
+      <c r="B55" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="5">
+        <v>90</v>
+      </c>
+      <c r="D55" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>89.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="43"/>
+      <c r="B56" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="5">
+        <v>14.5</v>
+      </c>
+      <c r="D56" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="43"/>
+      <c r="B57" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="5">
+        <v>8.6</v>
+      </c>
+      <c r="D57" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="43"/>
+      <c r="B58" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="5">
+        <v>76.5</v>
+      </c>
+      <c r="D58" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>75.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="43"/>
+      <c r="B59" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="5">
+        <v>39</v>
+      </c>
+      <c r="D59" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="43"/>
+      <c r="B60" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="5">
+        <v>7.6</v>
+      </c>
+      <c r="D60" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="43"/>
+      <c r="B61" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C61" s="5">
+        <v>12.8</v>
+      </c>
+      <c r="D61" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="43"/>
+      <c r="B62" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C62" s="5">
+        <v>11.8</v>
+      </c>
+      <c r="D62" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>11.700000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="43"/>
+      <c r="B63" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="5">
+        <v>72.8</v>
+      </c>
+      <c r="D63" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="43"/>
+      <c r="B64" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="D64" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>14.799999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="43"/>
+      <c r="B65" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="D65" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="43"/>
+      <c r="B66" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="5">
+        <v>101.7</v>
+      </c>
+      <c r="D66" s="47">
+        <f t="shared" ca="1" si="0"/>
+        <v>101.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="43"/>
+      <c r="B67" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="5">
+        <v>15.5</v>
+      </c>
+      <c r="D67" s="47">
+        <f t="shared" ref="D67" ca="1" si="1">C67-RANDBETWEEN(0, 10)/10</f>
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="44"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="46"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="44"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="46"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="44"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="44"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="46"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="44"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="46"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="44"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="46"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="44"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="46"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="44"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="46"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="44"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="46"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="44"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="46"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="44"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="46"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="44"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="46"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="44"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="46"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="44"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="46"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="44"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="44"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="46"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="44"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="46"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="44"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="46"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="44"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="46"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="44"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="46"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="44"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="46"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="44"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="46"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="44"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="46"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="44"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="46"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="44"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="46"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="44"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="46"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="44"/>
+      <c r="B94" s="45"/>
+      <c r="C94" s="46"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="44"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="46"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="44"/>
+      <c r="B96" s="45"/>
+      <c r="C96" s="46"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="44"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="46"/>
+    </row>
+    <row r="98" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="44"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="46"/>
+    </row>
+    <row r="99" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="38"/>
+      <c r="B99" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="40">
+        <f>SUM(C2:C98)</f>
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B106" s="61">
+        <v>2.0469999999999899</v>
+      </c>
+      <c r="C106" s="30">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B107" s="61">
+        <v>2.0479999999999898</v>
+      </c>
+      <c r="C107" s="30">
+        <v>171.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="61">
+        <v>2.0489999999999902</v>
+      </c>
+      <c r="C108" s="30">
+        <v>127.60000000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B109" s="61">
+        <v>2.0499999999999901</v>
+      </c>
+      <c r="C109" s="30">
+        <v>38.199999999999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B110" s="61">
+        <v>2.0509999999999899</v>
+      </c>
+      <c r="C110" s="30">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B111" s="61">
+        <v>2.0519999999999898</v>
+      </c>
+      <c r="C111" s="30">
+        <v>3.4000000000000004</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B112" s="61">
+        <v>2.0529999999999902</v>
+      </c>
+      <c r="C112" s="30">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B113" s="61">
+        <v>2.0539999999999901</v>
+      </c>
+      <c r="C113" s="30">
+        <v>21.200000000000003</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B114" s="61">
+        <v>2.0549999999999899</v>
+      </c>
+      <c r="C114" s="30">
+        <v>10.100000000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B115" s="61">
+        <v>2.0559999999999898</v>
+      </c>
+      <c r="C115" s="30">
+        <v>15.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="C3" s="30">
+        <v>79.899999999999991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="C4" s="30">
+        <v>64.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="C5" s="30">
+        <v>217.29999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2.004</v>
+      </c>
+      <c r="C6" s="30">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="C7" s="30">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2.0059999999999998</v>
+      </c>
+      <c r="C8" s="30">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2.008</v>
+      </c>
+      <c r="C9" s="30">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>2.0089999999999999</v>
+      </c>
+      <c r="C10" s="30">
+        <v>10.200000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="C11" s="30">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="C12" s="30">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13">
+        <v>2.012</v>
+      </c>
+      <c r="C13" s="56">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
+      <c r="B14" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="57">
+        <f>SUM(C3:C13)</f>
+        <v>546</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="43">
+        <v>1</v>
+      </c>
+      <c r="B15" s="13">
+        <v>2.0070000000000001</v>
+      </c>
+      <c r="C15" s="30">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="57">
+        <f>C15</f>
+        <v>18.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="C3" s="30">
+        <v>63.400000000000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="C4" s="30">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="C5" s="30">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2.016</v>
+      </c>
+      <c r="C6" s="30">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="C7" s="30">
+        <v>237.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2.0179999999999998</v>
+      </c>
+      <c r="C8" s="30">
+        <v>18.700000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2.0190000000000001</v>
+      </c>
+      <c r="C9" s="30">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="30">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13">
+        <v>2.0209999999999999</v>
+      </c>
+      <c r="C11" s="30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2.0589999999999899</v>
+      </c>
+      <c r="C12" s="30">
+        <v>3.5999999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="30">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
+      <c r="B14" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="57">
+        <f>SUM(C3:C13)</f>
+        <v>561.00000000000011</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2.0219999999999998</v>
+      </c>
+      <c r="C3" s="30">
+        <v>475.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>2.0230000000000001</v>
+      </c>
+      <c r="C4" s="30">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2.024</v>
+      </c>
+      <c r="C5" s="30">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="C6" s="30">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2.0259999999999998</v>
+      </c>
+      <c r="C7" s="30">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2.0270000000000001</v>
+      </c>
+      <c r="C8" s="30">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2.028</v>
+      </c>
+      <c r="C9" s="30">
+        <v>19.400000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>2.0289999999999999</v>
+      </c>
+      <c r="C10" s="30">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="C11" s="30">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2.0310000000000001</v>
+      </c>
+      <c r="C12" s="30">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13">
+        <v>2.032</v>
+      </c>
+      <c r="C13" s="30">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="43">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2.0339999999999998</v>
+      </c>
+      <c r="C14" s="63">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="43">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13">
+        <v>2.0350000000000001</v>
+      </c>
+      <c r="C15" s="63">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="43">
+        <v>14</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="63">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="43">
+        <v>15</v>
+      </c>
+      <c r="B17" s="13">
+        <v>2.06699999999999</v>
+      </c>
+      <c r="C17" s="63">
+        <v>90.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="43">
+        <v>16</v>
+      </c>
+      <c r="B18" s="13">
+        <v>2.0679999999999898</v>
+      </c>
+      <c r="C18" s="55">
+        <v>112.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="38"/>
+      <c r="B19" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="57">
+        <f>SUM(C3:C18)</f>
+        <v>867.5999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2.036</v>
+      </c>
+      <c r="C3" s="30">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>2.0390000000000001</v>
+      </c>
+      <c r="C4" s="30">
+        <v>62.099999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2.04</v>
+      </c>
+      <c r="C5" s="30">
+        <v>63.900000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2.0409999999999999</v>
+      </c>
+      <c r="C6" s="30">
+        <v>63.599999999999994</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2.0419999999999998</v>
+      </c>
+      <c r="C7" s="30">
+        <v>102.89999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2.0430000000000001</v>
+      </c>
+      <c r="C8" s="30">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2.044</v>
+      </c>
+      <c r="C9" s="30">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>2.0710000000000002</v>
+      </c>
+      <c r="C10" s="30">
+        <v>128.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="38"/>
+      <c r="B11" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="57">
+        <f>SUM(C3:C10)</f>
+        <v>535.40000000000009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>1</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2.0329999999999999</v>
+      </c>
+      <c r="C12" s="56">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="43">
+        <v>2</v>
+      </c>
+      <c r="B13" s="13">
+        <v>2.0369999999999999</v>
+      </c>
+      <c r="C13" s="56">
+        <v>541.20000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="43">
+        <v>3</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2.0379999999999998</v>
+      </c>
+      <c r="C14" s="56">
+        <v>65.300000000000011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="57">
+        <f>SUM(C12:C14)</f>
+        <v>639.10000000000014</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1087,11 +4354,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="44"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1200,11 +4467,3440 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2.0449999999999999</v>
+      </c>
+      <c r="C3" s="30">
+        <v>215.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13">
+        <v>2.04599999999999</v>
+      </c>
+      <c r="C4" s="30">
+        <v>163.20000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2.0469999999999899</v>
+      </c>
+      <c r="C5" s="30">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2.0479999999999898</v>
+      </c>
+      <c r="C6" s="30">
+        <v>171.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2.0489999999999902</v>
+      </c>
+      <c r="C7" s="30">
+        <v>127.60000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="30">
+        <v>38.199999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2.0509999999999899</v>
+      </c>
+      <c r="C9" s="30">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13">
+        <v>2.0519999999999898</v>
+      </c>
+      <c r="C10" s="30">
+        <v>3.4000000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13">
+        <v>2.0529999999999902</v>
+      </c>
+      <c r="C11" s="30">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2.0539999999999901</v>
+      </c>
+      <c r="C12" s="30">
+        <v>21.200000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="43">
+        <v>11</v>
+      </c>
+      <c r="B13" s="13">
+        <v>2.0549999999999899</v>
+      </c>
+      <c r="C13" s="30">
+        <v>10.100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="43">
+        <v>12</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2.0559999999999898</v>
+      </c>
+      <c r="C14" s="30">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="43">
+        <v>13</v>
+      </c>
+      <c r="B15" s="13">
+        <v>2.0689999999999902</v>
+      </c>
+      <c r="C15" s="30">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="B16" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="57">
+        <f>SUM(C3:C15)</f>
+        <v>836.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="64">
+        <v>1</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="65">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="57">
+        <f>C17</f>
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19">
+        <v>1</v>
+      </c>
+      <c r="E3" s="20">
+        <f>'1с'!C14+'2с'!C14+'3с'!C19+'4_5с'!C11+'6с'!C16</f>
+        <v>3346.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="33">
+        <f>E$3*D4</f>
+        <v>669.24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="33">
+        <f>E3/2.33</f>
+        <v>1436.137339055794</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="33">
+        <f>E$3*D6</f>
+        <v>3680.82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="33">
+        <f>E$3*D$7*0.065*1000</f>
+        <v>391505.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8</v>
+      </c>
+      <c r="E8" s="41">
+        <f>ROUNDUP(E$3*D8, 0)</f>
+        <v>26770</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20">
+        <f>'4_5с'!C15</f>
+        <v>639.10000000000014</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="33">
+        <f>E$9*D10</f>
+        <v>127.82000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="33">
+        <f>E9/2.33</f>
+        <v>274.29184549356228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E12" s="33">
+        <f t="shared" ref="E12" si="0">E$9*D12</f>
+        <v>703.01000000000022</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E13" s="33">
+        <f>E$9*D13*60</f>
+        <v>69022.800000000017</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>8</v>
+      </c>
+      <c r="E14" s="33">
+        <f>ROUNDUP(E$9*D14, 0)</f>
+        <v>5113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="19">
+        <v>1</v>
+      </c>
+      <c r="E15" s="20">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E16" s="33">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="33">
+        <v>15.519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E18" s="33">
+        <v>37.950000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E19" s="33">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="6">
+        <v>8</v>
+      </c>
+      <c r="E20" s="33">
+        <v>276</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="3" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:D231"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.140625" style="61"/>
+    <col min="3" max="3" width="9.140625" style="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="43"/>
+      <c r="C1" s="62">
+        <v>-0.5</v>
+      </c>
+      <c r="D1">
+        <f t="shared" ref="D1:D21" ca="1" si="0">C1- RANDBETWEEN(1, 10)/10</f>
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="43"/>
+      <c r="C2" s="62">
+        <v>-0.8</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="43"/>
+      <c r="C3" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="43"/>
+      <c r="C4" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ca="1" si="0"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="43"/>
+      <c r="C5" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="43"/>
+      <c r="B6" s="61">
+        <v>2.0059999999999998</v>
+      </c>
+      <c r="C6" s="30">
+        <v>41.7</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ca="1" si="0"/>
+        <v>41.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="43"/>
+      <c r="C7" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="43"/>
+      <c r="C8" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="C9" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="C10" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="43"/>
+      <c r="C11" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="43"/>
+      <c r="C12" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="43"/>
+      <c r="C13" s="30"/>
+      <c r="D13">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="43"/>
+      <c r="C14" s="30"/>
+      <c r="D14">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="43"/>
+      <c r="C15" s="30"/>
+      <c r="D15">
+        <f t="shared" ca="1" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="43"/>
+      <c r="C16" s="30"/>
+      <c r="D16">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="43"/>
+      <c r="C17" s="30"/>
+      <c r="D17">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="43"/>
+      <c r="C18" s="30"/>
+      <c r="D18">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="43"/>
+      <c r="C19" s="30"/>
+      <c r="D19">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="43"/>
+      <c r="C20" s="30"/>
+      <c r="D20">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="43"/>
+      <c r="C21" s="30"/>
+      <c r="D21">
+        <f t="shared" ca="1" si="0"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="43"/>
+      <c r="C45" s="30"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="43"/>
+      <c r="C46" s="30"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="43"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="43"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="43"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="43"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="43"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="43"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="43"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="43"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="43"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="43"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="43"/>
+      <c r="C57" s="30"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="43"/>
+      <c r="C58" s="30"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="43"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="43"/>
+      <c r="C60" s="30"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="43"/>
+      <c r="C61" s="30"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="43"/>
+      <c r="C62" s="30"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="43"/>
+      <c r="C63" s="30"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="43"/>
+      <c r="C64" s="30"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="43"/>
+      <c r="B65" s="61">
+        <v>2.0649999999999902</v>
+      </c>
+      <c r="C65" s="30">
+        <v>4</v>
+      </c>
+      <c r="D65">
+        <f ca="1">C65- RANDBETWEEN(1, 10)/10</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="43"/>
+      <c r="B66" s="61">
+        <v>2.0659999999999901</v>
+      </c>
+      <c r="C66" s="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="43"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="43"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="43"/>
+      <c r="C69" s="30"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="43"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="43"/>
+      <c r="C71" s="30"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="43"/>
+      <c r="B72" s="60"/>
+      <c r="C72" s="30"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="43"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="30"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="43"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="30"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="43"/>
+      <c r="B75" s="60"/>
+      <c r="C75" s="30"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="43"/>
+      <c r="B76" s="60"/>
+      <c r="C76" s="30"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="43"/>
+      <c r="B77" s="60"/>
+      <c r="C77" s="30"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="43"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="30"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="43"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="30"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="43"/>
+      <c r="B80" s="60"/>
+      <c r="C80" s="30"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="43"/>
+      <c r="B81" s="60"/>
+      <c r="C81" s="30"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="43"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="30"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="43"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="30"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="43"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="30"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="43"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="30"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="43"/>
+      <c r="B86" s="60"/>
+      <c r="C86" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D86">
+        <f t="shared" ref="D86:D117" ca="1" si="1">C86- RANDBETWEEN(1, 10)/10</f>
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="43"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D87">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="43"/>
+      <c r="B88" s="60"/>
+      <c r="C88" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D88">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="43"/>
+      <c r="B89" s="60"/>
+      <c r="C89" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D89">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="43"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D90">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="43"/>
+      <c r="B91" s="60"/>
+      <c r="C91" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D91">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="43"/>
+      <c r="B92" s="60"/>
+      <c r="C92" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D92">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="43"/>
+      <c r="B93" s="60"/>
+      <c r="C93" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D93">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="43"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D94">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="43"/>
+      <c r="B95" s="60"/>
+      <c r="C95" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D95">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="43"/>
+      <c r="B96" s="60"/>
+      <c r="C96" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D96">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="43"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D97">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="43"/>
+      <c r="B98" s="60"/>
+      <c r="C98" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D98">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="43"/>
+      <c r="B99" s="60"/>
+      <c r="C99" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D99">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="43"/>
+      <c r="B100" s="60"/>
+      <c r="C100" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D100">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="43"/>
+      <c r="B101" s="60"/>
+      <c r="C101" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D101">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="43"/>
+      <c r="B102" s="60"/>
+      <c r="C102" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D102">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="43"/>
+      <c r="B103" s="60"/>
+      <c r="C103" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D103">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="43"/>
+      <c r="B104" s="60"/>
+      <c r="C104" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D104">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="43"/>
+      <c r="B105" s="60"/>
+      <c r="C105" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D105">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="43"/>
+      <c r="B106" s="60"/>
+      <c r="C106" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D106">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="43"/>
+      <c r="B107" s="60"/>
+      <c r="C107" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D107">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="43"/>
+      <c r="B108" s="60"/>
+      <c r="C108" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D108">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="43"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D109">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="43"/>
+      <c r="B110" s="60"/>
+      <c r="C110" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D110">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="43"/>
+      <c r="B111" s="60"/>
+      <c r="C111" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D111">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="43"/>
+      <c r="B112" s="60"/>
+      <c r="C112" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D112">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="43"/>
+      <c r="B113" s="60"/>
+      <c r="C113" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D113">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="43"/>
+      <c r="B114" s="60"/>
+      <c r="C114" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D114">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="43"/>
+      <c r="B115" s="60"/>
+      <c r="C115" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D115">
+        <f t="shared" ca="1" si="1"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="43"/>
+      <c r="B116" s="60"/>
+      <c r="C116" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D116">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="43"/>
+      <c r="B117" s="60"/>
+      <c r="C117" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D117">
+        <f t="shared" ca="1" si="1"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="43"/>
+      <c r="B118" s="60"/>
+      <c r="C118" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D118">
+        <f t="shared" ref="D118:D149" ca="1" si="2">C118- RANDBETWEEN(1, 10)/10</f>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="43"/>
+      <c r="B119" s="60"/>
+      <c r="C119" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D119">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="43"/>
+      <c r="B120" s="60"/>
+      <c r="C120" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D120">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.2999999999999998</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="43"/>
+      <c r="B121" s="60"/>
+      <c r="C121" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D121">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="43"/>
+      <c r="B122" s="60"/>
+      <c r="C122" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D122">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="43"/>
+      <c r="B123" s="60"/>
+      <c r="C123" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D123">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="43"/>
+      <c r="B124" s="60"/>
+      <c r="C124" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D124">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="43"/>
+      <c r="B125" s="60"/>
+      <c r="C125" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D125">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="43"/>
+      <c r="B126" s="60"/>
+      <c r="C126" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D126">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="43"/>
+      <c r="B127" s="60"/>
+      <c r="C127" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D127">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="43"/>
+      <c r="B128" s="60"/>
+      <c r="C128" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D128">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="43"/>
+      <c r="B129" s="60"/>
+      <c r="C129" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D129">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="43"/>
+      <c r="B130" s="60"/>
+      <c r="C130" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D130">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="43"/>
+      <c r="B131" s="60"/>
+      <c r="C131" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D131">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="43"/>
+      <c r="B132" s="60"/>
+      <c r="C132" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D132">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="43"/>
+      <c r="B133" s="60"/>
+      <c r="C133" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D133">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="43"/>
+      <c r="B134" s="60"/>
+      <c r="C134" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D134">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="43"/>
+      <c r="B135" s="60"/>
+      <c r="C135" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D135">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="43"/>
+      <c r="B136" s="60"/>
+      <c r="C136" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D136">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="43"/>
+      <c r="B137" s="60"/>
+      <c r="C137" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D137">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="43"/>
+      <c r="B138" s="60"/>
+      <c r="C138" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D138">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.79999999999999993</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="43"/>
+      <c r="B139" s="60"/>
+      <c r="C139" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D139">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="43"/>
+      <c r="B140" s="60"/>
+      <c r="C140" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D140">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="43"/>
+      <c r="B141" s="60"/>
+      <c r="C141" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D141">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="43"/>
+      <c r="B142" s="60"/>
+      <c r="C142" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D142">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="43"/>
+      <c r="B143" s="60"/>
+      <c r="C143" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D143">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="43"/>
+      <c r="B144" s="60"/>
+      <c r="C144" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D144">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="43"/>
+      <c r="B145" s="60"/>
+      <c r="C145" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D145">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="43"/>
+      <c r="B146" s="60"/>
+      <c r="C146" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D146">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="43"/>
+      <c r="B147" s="60"/>
+      <c r="C147" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D147">
+        <f t="shared" ca="1" si="2"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="43"/>
+      <c r="B148" s="60"/>
+      <c r="C148" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D148">
+        <f t="shared" ca="1" si="2"/>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="43"/>
+      <c r="B149" s="60"/>
+      <c r="C149" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D149">
+        <f t="shared" ca="1" si="2"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="43"/>
+      <c r="B150" s="60"/>
+      <c r="C150" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D150">
+        <f t="shared" ref="D150:D181" ca="1" si="3">C150- RANDBETWEEN(1, 10)/10</f>
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="43"/>
+      <c r="B151" s="60"/>
+      <c r="C151" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D151">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="43"/>
+      <c r="B152" s="60"/>
+      <c r="C152" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D152">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="43"/>
+      <c r="B153" s="60"/>
+      <c r="C153" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D153">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="43"/>
+      <c r="B154" s="60"/>
+      <c r="C154" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D154">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.2999999999999998</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="43"/>
+      <c r="B155" s="60"/>
+      <c r="C155" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D155">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="43"/>
+      <c r="B156" s="60"/>
+      <c r="C156" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D156">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="43"/>
+      <c r="B157" s="60"/>
+      <c r="C157" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D157">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="43"/>
+      <c r="B158" s="60"/>
+      <c r="C158" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D158">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="43"/>
+      <c r="B159" s="60"/>
+      <c r="C159" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D159">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="43"/>
+      <c r="B160" s="60"/>
+      <c r="C160" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D160">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="43"/>
+      <c r="B161" s="60"/>
+      <c r="C161" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D161">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="43"/>
+      <c r="B162" s="60"/>
+      <c r="C162" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D162">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="43"/>
+      <c r="B163" s="60"/>
+      <c r="C163" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D163">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="43"/>
+      <c r="B164" s="60"/>
+      <c r="C164" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D164">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="43"/>
+      <c r="B165" s="60"/>
+      <c r="C165" s="30">
+        <v>-0.2</v>
+      </c>
+      <c r="D165">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="43"/>
+      <c r="B166" s="60"/>
+      <c r="C166" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D166">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="43"/>
+      <c r="B167" s="60"/>
+      <c r="C167" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D167">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="43"/>
+      <c r="B168" s="60"/>
+      <c r="C168" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D168">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="43"/>
+      <c r="B169" s="60"/>
+      <c r="C169" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D169">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="43"/>
+      <c r="B170" s="60"/>
+      <c r="C170" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D170">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="43"/>
+      <c r="B171" s="60"/>
+      <c r="C171" s="30">
+        <v>-0.3</v>
+      </c>
+      <c r="D171">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="43"/>
+      <c r="B172" s="60"/>
+      <c r="C172" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D172">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="43"/>
+      <c r="B173" s="60"/>
+      <c r="C173" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D173">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="43"/>
+      <c r="B174" s="60"/>
+      <c r="C174" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D174">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="43"/>
+      <c r="B175" s="60"/>
+      <c r="C175" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D175">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="43"/>
+      <c r="B176" s="60"/>
+      <c r="C176" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D176">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="43"/>
+      <c r="B177" s="60"/>
+      <c r="C177" s="30">
+        <v>-0.6</v>
+      </c>
+      <c r="D177">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.2999999999999998</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="43"/>
+      <c r="B178" s="60"/>
+      <c r="C178" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D178">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.7000000000000002</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="43"/>
+      <c r="B179" s="60"/>
+      <c r="C179" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D179">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="43"/>
+      <c r="B180" s="60"/>
+      <c r="C180" s="30">
+        <v>-0.5</v>
+      </c>
+      <c r="D180">
+        <f t="shared" ca="1" si="3"/>
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="43"/>
+      <c r="B181" s="60"/>
+      <c r="C181" s="30">
+        <v>-0.4</v>
+      </c>
+      <c r="D181">
+        <f t="shared" ca="1" si="3"/>
+        <v>-0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="43"/>
+      <c r="B182" s="60"/>
+      <c r="C182" s="30">
+        <v>-0.7</v>
+      </c>
+      <c r="D182">
+        <f t="shared" ref="D182:D189" ca="1" si="4">C182- RANDBETWEEN(1, 10)/10</f>
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="43"/>
+      <c r="B183" s="60"/>
+      <c r="C183" s="30">
+        <v>-0.8</v>
+      </c>
+      <c r="D183">
+        <f t="shared" ca="1" si="4"/>
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="43"/>
+      <c r="B184" s="60"/>
+      <c r="C184" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D184">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="43"/>
+      <c r="B185" s="60"/>
+      <c r="C185" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D185">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="43"/>
+      <c r="B186" s="60"/>
+      <c r="C186" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D186">
+        <f t="shared" ca="1" si="4"/>
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="43"/>
+      <c r="B187" s="60"/>
+      <c r="C187" s="30">
+        <v>-0.1</v>
+      </c>
+      <c r="D187">
+        <f t="shared" ca="1" si="4"/>
+        <v>-1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="43"/>
+      <c r="B188" s="60"/>
+      <c r="C188" s="30">
+        <v>-1</v>
+      </c>
+      <c r="D188">
+        <f t="shared" ca="1" si="4"/>
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="43"/>
+      <c r="B189" s="60"/>
+      <c r="C189" s="30">
+        <v>-0.9</v>
+      </c>
+      <c r="D189">
+        <f t="shared" ca="1" si="4"/>
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="43"/>
+      <c r="B190" s="60"/>
+      <c r="C190" s="30"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="43"/>
+      <c r="B191" s="60"/>
+      <c r="C191" s="30"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="43"/>
+      <c r="B192" s="60"/>
+      <c r="C192" s="30"/>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="43"/>
+      <c r="B193" s="60"/>
+      <c r="C193" s="30"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="43"/>
+      <c r="B194" s="60"/>
+      <c r="C194" s="30"/>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="43"/>
+      <c r="B195" s="60"/>
+      <c r="C195" s="30"/>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="43"/>
+      <c r="B196" s="60"/>
+      <c r="C196" s="30"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="43"/>
+      <c r="B197" s="60"/>
+      <c r="C197" s="30"/>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="43"/>
+      <c r="B198" s="60"/>
+      <c r="C198" s="30"/>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="43"/>
+      <c r="B199" s="60"/>
+      <c r="C199" s="30"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="43"/>
+      <c r="B200" s="60"/>
+      <c r="C200" s="30"/>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="43"/>
+      <c r="B201" s="60"/>
+      <c r="C201" s="30"/>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="43"/>
+      <c r="B202" s="60"/>
+      <c r="C202" s="30"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="43"/>
+      <c r="B203" s="60"/>
+      <c r="C203" s="30"/>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="43"/>
+      <c r="B204" s="60"/>
+      <c r="C204" s="30"/>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="43"/>
+      <c r="B205" s="60"/>
+      <c r="C205" s="30"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="43"/>
+      <c r="B206" s="60"/>
+      <c r="C206" s="30"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="43"/>
+      <c r="B207" s="60"/>
+      <c r="C207" s="30"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="43"/>
+      <c r="B208" s="60"/>
+      <c r="C208" s="30"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="43"/>
+      <c r="B209" s="60"/>
+      <c r="C209" s="30"/>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="43"/>
+      <c r="B210" s="60"/>
+      <c r="C210" s="30"/>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="43"/>
+      <c r="B211" s="60"/>
+      <c r="C211" s="30"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="43"/>
+      <c r="B212" s="60"/>
+      <c r="C212" s="30"/>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="43"/>
+      <c r="B213" s="60"/>
+      <c r="C213" s="30"/>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="43"/>
+      <c r="B214" s="60"/>
+      <c r="C214" s="30"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="43"/>
+      <c r="B215" s="60"/>
+      <c r="C215" s="30"/>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="43"/>
+      <c r="B216" s="60"/>
+      <c r="C216" s="30"/>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="43"/>
+      <c r="B217" s="60"/>
+      <c r="C217" s="30"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="43"/>
+      <c r="B218" s="60"/>
+      <c r="C218" s="30"/>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="43"/>
+      <c r="B219" s="60"/>
+      <c r="C219" s="30"/>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="43"/>
+      <c r="B220" s="60"/>
+      <c r="C220" s="30"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="43"/>
+      <c r="B221" s="60"/>
+      <c r="C221" s="30"/>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="43"/>
+      <c r="B222" s="60"/>
+      <c r="C222" s="30"/>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="43"/>
+      <c r="B223" s="60"/>
+      <c r="C223" s="30"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="43"/>
+      <c r="B224" s="60"/>
+      <c r="C224" s="30"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="43"/>
+      <c r="B225" s="60"/>
+      <c r="C225" s="30"/>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="43"/>
+      <c r="B226" s="60"/>
+      <c r="C226" s="30"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="43"/>
+      <c r="B227" s="60"/>
+      <c r="C227" s="30"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="43"/>
+      <c r="B228" s="60"/>
+      <c r="C228" s="30"/>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="43"/>
+      <c r="B229" s="60"/>
+      <c r="C229" s="30"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="43"/>
+      <c r="B230" s="60"/>
+      <c r="C230" s="30"/>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="43"/>
+      <c r="B231" s="60"/>
+      <c r="C231" s="30"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19">
+        <v>1</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="33">
+        <f>E$3*D4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="33">
+        <f>E$3*D6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="33">
+        <f>E$3*D$7*0.065*1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8</v>
+      </c>
+      <c r="E8" s="41">
+        <f>ROUNDUP(E$3*D8, 0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="7">
+        <v>171.6</v>
+      </c>
+      <c r="D3" s="42"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7">
+        <v>128.30000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="7">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="7">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="7">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="35">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="37">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="35">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="37">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="35">
+        <v>9</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="37">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="38"/>
+      <c r="B12" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="40">
+        <f>SUM(C3:C11)</f>
+        <v>418.28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="7">
+        <v>216.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="7">
+        <v>163.30000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="7">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
+      <c r="B6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="40">
+        <f>SUM(C3:C5)</f>
+        <v>421.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="7"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="7"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="35">
+        <v>7</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="37"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="35">
+        <v>8</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="37"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="35">
+        <v>9</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="37"/>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
+      <c r="B16" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="40">
+        <f>SUM(C3:C15)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="68"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="7">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="7">
+        <v>65.400000000000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="7">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="7">
+        <v>64.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="7">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="7">
+        <v>103.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="37">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="37">
+        <v>163.30000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="37">
+        <v>128.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="35">
+        <v>10</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="37">
+        <v>15.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="40">
+        <f>SUM(C3:C12)</f>
+        <v>765.87</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="19">
+        <v>1</v>
+      </c>
+      <c r="E3" s="20">
+        <f>'7сэ3'!C13+'6с3э'!C16+'4с3э'!C15+'3с3э'!C13+'2с3э'!C14+'1с3'!C11</f>
+        <v>3879.63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="33">
+        <f>E$3*D4</f>
+        <v>775.92600000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="33">
+        <f>E3/2.33</f>
+        <v>1665.0772532188842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E6" s="33">
+        <f>E$3*D6</f>
+        <v>4267.5930000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E7" s="33">
+        <f>E$3*D$7*0.065*1000</f>
+        <v>453916.71000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8</v>
+      </c>
+      <c r="E8" s="41">
+        <f>ROUNDUP(E$3*D8, 0)</f>
+        <v>31038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="19">
+        <v>1</v>
+      </c>
+      <c r="E9" s="20">
+        <f>'7сэ3'!C16</f>
+        <v>238.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="33">
+        <f>E$9*D10</f>
+        <v>47.760000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="33">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E12" s="33">
+        <f t="shared" ref="E12:E14" si="0">E$9*D12</f>
+        <v>262.68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E13" s="33">
+        <f>E$9*D13*60</f>
+        <v>25790.400000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>8</v>
+      </c>
+      <c r="E14" s="33">
+        <f t="shared" si="0"/>
+        <v>1910.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="69" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="56">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="43">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="55">
+        <v>155.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="55">
+        <v>197.29999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="55">
+        <v>9.129999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="55">
+        <v>89.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="30">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="55">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="55">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="43">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="55">
+        <v>11.200000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="43">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="55">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="57">
+        <f>SUM(C3:C12)</f>
+        <v>611.53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="43">
+        <v>1</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="58">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="43">
+        <v>2</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="58">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="58">
+        <f>SUM(C14:C15)</f>
+        <v>238.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/school_2/vor_spartac_2_floors.xlsx
+++ b/school_2/vor_spartac_2_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="858" firstSheet="5" activeTab="16"/>
+    <workbookView xWindow="480" yWindow="30" windowWidth="19155" windowHeight="8520" tabRatio="858" firstSheet="7" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="7 с" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,6 @@
     <sheet name="4_5с" sheetId="22" r:id="rId19"/>
     <sheet name="6с" sheetId="23" r:id="rId20"/>
     <sheet name="Вор2э" sheetId="24" r:id="rId21"/>
-    <sheet name="Лист1" sheetId="17" r:id="rId22"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
@@ -931,7 +930,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1108,13 +1107,7 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1663,11 +1656,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -1850,11 +1843,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2026,11 +2019,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2180,11 +2173,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2345,11 +2338,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -2504,7 +2497,7 @@
       </c>
       <c r="D2" s="47">
         <f ca="1">C2-RANDBETWEEN(0, 10)/10</f>
-        <v>79.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2517,7 +2510,7 @@
       </c>
       <c r="D3" s="47">
         <f t="shared" ref="D3:D66" ca="1" si="0">C3-RANDBETWEEN(0, 10)/10</f>
-        <v>63.3</v>
+        <v>62.699999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2543,7 +2536,7 @@
       </c>
       <c r="D5" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>244</v>
+        <v>244.3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2556,7 +2549,7 @@
       </c>
       <c r="D6" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>18.299999999999997</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2569,7 +2562,7 @@
       </c>
       <c r="D7" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5</v>
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2582,7 +2575,7 @@
       </c>
       <c r="D8" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2595,7 +2588,7 @@
       </c>
       <c r="D9" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>3.7</v>
+        <v>4.1000000000000005</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2608,7 +2601,7 @@
       </c>
       <c r="D10" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2621,7 +2614,7 @@
       </c>
       <c r="D11" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>102.8</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2634,7 +2627,7 @@
       </c>
       <c r="D12" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2647,7 +2640,7 @@
       </c>
       <c r="D13" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>234.79999999999998</v>
+        <v>235.2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2673,7 +2666,7 @@
       </c>
       <c r="D15" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.2</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,7 +2679,7 @@
       </c>
       <c r="D16" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>19.3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2699,7 +2692,7 @@
       </c>
       <c r="D17" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2712,7 +2705,7 @@
       </c>
       <c r="D18" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>10.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2725,7 +2718,7 @@
       </c>
       <c r="D19" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2751,7 +2744,7 @@
       </c>
       <c r="D21" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>28.2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2764,7 +2757,7 @@
       </c>
       <c r="D22" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>23.7</v>
+        <v>24.099999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2777,7 +2770,7 @@
       </c>
       <c r="D23" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>74.900000000000006</v>
+        <v>74.800000000000011</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2790,7 +2783,7 @@
       </c>
       <c r="D24" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>188.29999999999998</v>
+        <v>188.2</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2803,7 +2796,7 @@
       </c>
       <c r="D25" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2829,7 +2822,7 @@
       </c>
       <c r="D27" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2842,7 +2835,7 @@
       </c>
       <c r="D28" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>89.3</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2855,7 +2848,7 @@
       </c>
       <c r="D29" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>62.5</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2868,7 +2861,7 @@
       </c>
       <c r="D30" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,7 +2874,7 @@
       </c>
       <c r="D31" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.699999999999996</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2894,7 +2887,7 @@
       </c>
       <c r="D32" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.2</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2907,7 +2900,7 @@
       </c>
       <c r="D33" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>63.399999999999991</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2920,7 +2913,7 @@
       </c>
       <c r="D34" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>8.2999999999999989</v>
+        <v>8.8999999999999986</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2933,7 +2926,7 @@
       </c>
       <c r="D35" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2946,7 +2939,7 @@
       </c>
       <c r="D36" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>62.3</v>
+        <v>63.199999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2959,7 +2952,7 @@
       </c>
       <c r="D37" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2972,7 +2965,7 @@
       </c>
       <c r="D38" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>115.60000000000001</v>
+        <v>115.80000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2998,7 +2991,7 @@
       </c>
       <c r="D40" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>19.5</v>
+        <v>20.399999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3011,7 +3004,7 @@
       </c>
       <c r="D41" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>120.10000000000001</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3024,7 +3017,7 @@
       </c>
       <c r="D42" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>165.20000000000002</v>
+        <v>165.8</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3037,7 +3030,7 @@
       </c>
       <c r="D43" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>22.099999999999998</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3050,7 +3043,7 @@
       </c>
       <c r="D44" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3063,7 +3056,7 @@
       </c>
       <c r="D45" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>4.1000000000000005</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3076,7 +3069,7 @@
       </c>
       <c r="D46" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8</v>
+        <v>5.1999999999999993</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3089,7 +3082,7 @@
       </c>
       <c r="D47" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <v>8.7999999999999989</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3102,7 +3095,7 @@
       </c>
       <c r="D48" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>9.1999999999999993</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3115,7 +3108,7 @@
       </c>
       <c r="D49" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>93.9</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3128,7 +3121,7 @@
       </c>
       <c r="D50" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>40.199999999999996</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3141,7 +3134,7 @@
       </c>
       <c r="D51" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>155.6</v>
+        <v>155.80000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3154,7 +3147,7 @@
       </c>
       <c r="D52" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>197.29999999999998</v>
+        <v>197.2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3180,7 +3173,7 @@
       </c>
       <c r="D54" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>200.4</v>
+        <v>200.9</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3193,7 +3186,7 @@
       </c>
       <c r="D55" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>89.7</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3206,7 +3199,7 @@
       </c>
       <c r="D56" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>13.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3219,7 +3212,7 @@
       </c>
       <c r="D57" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>7.8</v>
+        <v>7.8999999999999995</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3232,7 +3225,7 @@
       </c>
       <c r="D58" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>75.8</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3245,7 +3238,7 @@
       </c>
       <c r="D59" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3258,7 +3251,7 @@
       </c>
       <c r="D60" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>7.6</v>
+        <v>7.1999999999999993</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3271,7 +3264,7 @@
       </c>
       <c r="D61" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>11.8</v>
+        <v>12.200000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3284,7 +3277,7 @@
       </c>
       <c r="D62" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>11.700000000000001</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3297,7 +3290,7 @@
       </c>
       <c r="D63" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>72.099999999999994</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3323,7 +3316,7 @@
       </c>
       <c r="D65" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3349,7 +3342,7 @@
       </c>
       <c r="D67" s="47">
         <f t="shared" ref="D67" ca="1" si="1">C67-RANDBETWEEN(0, 10)/10</f>
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3518,7 +3511,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="61">
+      <c r="B106" s="60">
         <v>2.0469999999999899</v>
       </c>
       <c r="C106" s="30">
@@ -3526,7 +3519,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="61">
+      <c r="B107" s="60">
         <v>2.0479999999999898</v>
       </c>
       <c r="C107" s="30">
@@ -3534,7 +3527,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="61">
+      <c r="B108" s="60">
         <v>2.0489999999999902</v>
       </c>
       <c r="C108" s="30">
@@ -3542,7 +3535,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="61">
+      <c r="B109" s="60">
         <v>2.0499999999999901</v>
       </c>
       <c r="C109" s="30">
@@ -3550,7 +3543,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="61">
+      <c r="B110" s="60">
         <v>2.0509999999999899</v>
       </c>
       <c r="C110" s="30">
@@ -3558,7 +3551,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B111" s="61">
+      <c r="B111" s="60">
         <v>2.0519999999999898</v>
       </c>
       <c r="C111" s="30">
@@ -3566,7 +3559,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="61">
+      <c r="B112" s="60">
         <v>2.0529999999999902</v>
       </c>
       <c r="C112" s="30">
@@ -3574,7 +3567,7 @@
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B113" s="61">
+      <c r="B113" s="60">
         <v>2.0539999999999901</v>
       </c>
       <c r="C113" s="30">
@@ -3582,7 +3575,7 @@
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B114" s="61">
+      <c r="B114" s="60">
         <v>2.0549999999999899</v>
       </c>
       <c r="C114" s="30">
@@ -3590,7 +3583,7 @@
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B115" s="61">
+      <c r="B115" s="60">
         <v>2.0559999999999898</v>
       </c>
       <c r="C115" s="30">
@@ -3608,11 +3601,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -3793,11 +3786,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -3955,11 +3948,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -4100,7 +4093,7 @@
       <c r="B14" s="13">
         <v>2.0339999999999998</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="61">
         <v>7.8</v>
       </c>
     </row>
@@ -4111,7 +4104,7 @@
       <c r="B15" s="13">
         <v>2.0350000000000001</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="61">
         <v>7.4</v>
       </c>
     </row>
@@ -4122,7 +4115,7 @@
       <c r="B16" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="61">
         <v>3.9</v>
       </c>
     </row>
@@ -4133,7 +4126,7 @@
       <c r="B17" s="13">
         <v>2.06699999999999</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="61">
         <v>90.1</v>
       </c>
     </row>
@@ -4172,11 +4165,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -4354,11 +4347,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -4473,11 +4466,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -4644,13 +4637,13 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="64">
+      <c r="A17" s="62">
         <v>1</v>
       </c>
       <c r="B17" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="63">
         <v>16</v>
       </c>
     </row>
@@ -5038,1751 +5031,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:D231"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="9.140625" style="61"/>
-    <col min="3" max="3" width="9.140625" style="62"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="C1" s="62">
-        <v>-0.5</v>
-      </c>
-      <c r="D1">
-        <f t="shared" ref="D1:D21" ca="1" si="0">C1- RANDBETWEEN(1, 10)/10</f>
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="C2" s="62">
-        <v>-0.8</v>
-      </c>
-      <c r="D2">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="C3" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="C4" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ca="1" si="0"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="C5" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="61">
-        <v>2.0059999999999998</v>
-      </c>
-      <c r="C6" s="30">
-        <v>41.7</v>
-      </c>
-      <c r="D6">
-        <f t="shared" ca="1" si="0"/>
-        <v>41.400000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
-      <c r="C7" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
-      <c r="C8" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D8">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="C9" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D9">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
-      <c r="C10" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D10">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
-      <c r="C11" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D11">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="43"/>
-      <c r="C12" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D12">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
-      <c r="C13" s="30"/>
-      <c r="D13">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="C14" s="30"/>
-      <c r="D14">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
-      <c r="C15" s="30"/>
-      <c r="D15">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
-      <c r="C16" s="30"/>
-      <c r="D16">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
-      <c r="C17" s="30"/>
-      <c r="D17">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="43"/>
-      <c r="C18" s="30"/>
-      <c r="D18">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="43"/>
-      <c r="C19" s="30"/>
-      <c r="D19">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="43"/>
-      <c r="C20" s="30"/>
-      <c r="D20">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="43"/>
-      <c r="C21" s="30"/>
-      <c r="D21">
-        <f t="shared" ca="1" si="0"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="43"/>
-      <c r="C45" s="30"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="43"/>
-      <c r="C46" s="30"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="43"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="43"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="43"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="43"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="43"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="43"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="43"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="43"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="43"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="43"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="43"/>
-      <c r="C57" s="30"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
-      <c r="C58" s="30"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="43"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="43"/>
-      <c r="C60" s="30"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="43"/>
-      <c r="C61" s="30"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="43"/>
-      <c r="C62" s="30"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="43"/>
-      <c r="C63" s="30"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="43"/>
-      <c r="C64" s="30"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="43"/>
-      <c r="B65" s="61">
-        <v>2.0649999999999902</v>
-      </c>
-      <c r="C65" s="30">
-        <v>4</v>
-      </c>
-      <c r="D65">
-        <f ca="1">C65- RANDBETWEEN(1, 10)/10</f>
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="43"/>
-      <c r="B66" s="61">
-        <v>2.0659999999999901</v>
-      </c>
-      <c r="C66" s="30">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="43"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="43"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="43"/>
-      <c r="C69" s="30"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="43"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="43"/>
-      <c r="C71" s="30"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="43"/>
-      <c r="B72" s="60"/>
-      <c r="C72" s="30"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="43"/>
-      <c r="B73" s="60"/>
-      <c r="C73" s="30"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="43"/>
-      <c r="B74" s="60"/>
-      <c r="C74" s="30"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="43"/>
-      <c r="B75" s="60"/>
-      <c r="C75" s="30"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="43"/>
-      <c r="B76" s="60"/>
-      <c r="C76" s="30"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="43"/>
-      <c r="B77" s="60"/>
-      <c r="C77" s="30"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="43"/>
-      <c r="B78" s="60"/>
-      <c r="C78" s="30"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="43"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="30"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="43"/>
-      <c r="B80" s="60"/>
-      <c r="C80" s="30"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="43"/>
-      <c r="B81" s="60"/>
-      <c r="C81" s="30"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="43"/>
-      <c r="B82" s="60"/>
-      <c r="C82" s="30"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="43"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="30"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="43"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="30"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="43"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="30"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="43"/>
-      <c r="B86" s="60"/>
-      <c r="C86" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D86">
-        <f t="shared" ref="D86:D117" ca="1" si="1">C86- RANDBETWEEN(1, 10)/10</f>
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="43"/>
-      <c r="B87" s="60"/>
-      <c r="C87" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D87">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="43"/>
-      <c r="B88" s="60"/>
-      <c r="C88" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D88">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="43"/>
-      <c r="B89" s="60"/>
-      <c r="C89" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D89">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="43"/>
-      <c r="B90" s="60"/>
-      <c r="C90" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D90">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="43"/>
-      <c r="B91" s="60"/>
-      <c r="C91" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D91">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="43"/>
-      <c r="B92" s="60"/>
-      <c r="C92" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D92">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="43"/>
-      <c r="B93" s="60"/>
-      <c r="C93" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D93">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="43"/>
-      <c r="B94" s="60"/>
-      <c r="C94" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D94">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="43"/>
-      <c r="B95" s="60"/>
-      <c r="C95" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D95">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="43"/>
-      <c r="B96" s="60"/>
-      <c r="C96" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D96">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="43"/>
-      <c r="B97" s="60"/>
-      <c r="C97" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D97">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="43"/>
-      <c r="B98" s="60"/>
-      <c r="C98" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D98">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="43"/>
-      <c r="B99" s="60"/>
-      <c r="C99" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D99">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="43"/>
-      <c r="B100" s="60"/>
-      <c r="C100" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D100">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="43"/>
-      <c r="B101" s="60"/>
-      <c r="C101" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D101">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="43"/>
-      <c r="B102" s="60"/>
-      <c r="C102" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D102">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="43"/>
-      <c r="B103" s="60"/>
-      <c r="C103" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D103">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="43"/>
-      <c r="B104" s="60"/>
-      <c r="C104" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D104">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="43"/>
-      <c r="B105" s="60"/>
-      <c r="C105" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D105">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="43"/>
-      <c r="B106" s="60"/>
-      <c r="C106" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D106">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="43"/>
-      <c r="B107" s="60"/>
-      <c r="C107" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D107">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="43"/>
-      <c r="B108" s="60"/>
-      <c r="C108" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D108">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="43"/>
-      <c r="B109" s="60"/>
-      <c r="C109" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D109">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="43"/>
-      <c r="B110" s="60"/>
-      <c r="C110" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D110">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="43"/>
-      <c r="B111" s="60"/>
-      <c r="C111" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D111">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="43"/>
-      <c r="B112" s="60"/>
-      <c r="C112" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D112">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.79999999999999993</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="43"/>
-      <c r="B113" s="60"/>
-      <c r="C113" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D113">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="43"/>
-      <c r="B114" s="60"/>
-      <c r="C114" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D114">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="43"/>
-      <c r="B115" s="60"/>
-      <c r="C115" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D115">
-        <f t="shared" ca="1" si="1"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="43"/>
-      <c r="B116" s="60"/>
-      <c r="C116" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D116">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="43"/>
-      <c r="B117" s="60"/>
-      <c r="C117" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D117">
-        <f t="shared" ca="1" si="1"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="43"/>
-      <c r="B118" s="60"/>
-      <c r="C118" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D118">
-        <f t="shared" ref="D118:D149" ca="1" si="2">C118- RANDBETWEEN(1, 10)/10</f>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="43"/>
-      <c r="B119" s="60"/>
-      <c r="C119" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D119">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="43"/>
-      <c r="B120" s="60"/>
-      <c r="C120" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D120">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.2999999999999998</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="43"/>
-      <c r="B121" s="60"/>
-      <c r="C121" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D121">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="43"/>
-      <c r="B122" s="60"/>
-      <c r="C122" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D122">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="43"/>
-      <c r="B123" s="60"/>
-      <c r="C123" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D123">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="43"/>
-      <c r="B124" s="60"/>
-      <c r="C124" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D124">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="43"/>
-      <c r="B125" s="60"/>
-      <c r="C125" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D125">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="43"/>
-      <c r="B126" s="60"/>
-      <c r="C126" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D126">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="43"/>
-      <c r="B127" s="60"/>
-      <c r="C127" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D127">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="43"/>
-      <c r="B128" s="60"/>
-      <c r="C128" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D128">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="43"/>
-      <c r="B129" s="60"/>
-      <c r="C129" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D129">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="43"/>
-      <c r="B130" s="60"/>
-      <c r="C130" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D130">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.79999999999999993</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="43"/>
-      <c r="B131" s="60"/>
-      <c r="C131" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D131">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="43"/>
-      <c r="B132" s="60"/>
-      <c r="C132" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D132">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="43"/>
-      <c r="B133" s="60"/>
-      <c r="C133" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D133">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="43"/>
-      <c r="B134" s="60"/>
-      <c r="C134" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D134">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="43"/>
-      <c r="B135" s="60"/>
-      <c r="C135" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D135">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="43"/>
-      <c r="B136" s="60"/>
-      <c r="C136" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D136">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="43"/>
-      <c r="B137" s="60"/>
-      <c r="C137" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D137">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="43"/>
-      <c r="B138" s="60"/>
-      <c r="C138" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D138">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.79999999999999993</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="43"/>
-      <c r="B139" s="60"/>
-      <c r="C139" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D139">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="43"/>
-      <c r="B140" s="60"/>
-      <c r="C140" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D140">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="43"/>
-      <c r="B141" s="60"/>
-      <c r="C141" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D141">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="43"/>
-      <c r="B142" s="60"/>
-      <c r="C142" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D142">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="43"/>
-      <c r="B143" s="60"/>
-      <c r="C143" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D143">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="43"/>
-      <c r="B144" s="60"/>
-      <c r="C144" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D144">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="43"/>
-      <c r="B145" s="60"/>
-      <c r="C145" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D145">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="43"/>
-      <c r="B146" s="60"/>
-      <c r="C146" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D146">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="43"/>
-      <c r="B147" s="60"/>
-      <c r="C147" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D147">
-        <f t="shared" ca="1" si="2"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="43"/>
-      <c r="B148" s="60"/>
-      <c r="C148" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D148">
-        <f t="shared" ca="1" si="2"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="43"/>
-      <c r="B149" s="60"/>
-      <c r="C149" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D149">
-        <f t="shared" ca="1" si="2"/>
-        <v>-0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="43"/>
-      <c r="B150" s="60"/>
-      <c r="C150" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D150">
-        <f t="shared" ref="D150:D181" ca="1" si="3">C150- RANDBETWEEN(1, 10)/10</f>
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="43"/>
-      <c r="B151" s="60"/>
-      <c r="C151" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D151">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="43"/>
-      <c r="B152" s="60"/>
-      <c r="C152" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D152">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="43"/>
-      <c r="B153" s="60"/>
-      <c r="C153" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D153">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="43"/>
-      <c r="B154" s="60"/>
-      <c r="C154" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D154">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.2999999999999998</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="43"/>
-      <c r="B155" s="60"/>
-      <c r="C155" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D155">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="43"/>
-      <c r="B156" s="60"/>
-      <c r="C156" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D156">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="43"/>
-      <c r="B157" s="60"/>
-      <c r="C157" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D157">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="43"/>
-      <c r="B158" s="60"/>
-      <c r="C158" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D158">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="43"/>
-      <c r="B159" s="60"/>
-      <c r="C159" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D159">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="43"/>
-      <c r="B160" s="60"/>
-      <c r="C160" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D160">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="43"/>
-      <c r="B161" s="60"/>
-      <c r="C161" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D161">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="43"/>
-      <c r="B162" s="60"/>
-      <c r="C162" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D162">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="43"/>
-      <c r="B163" s="60"/>
-      <c r="C163" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D163">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="43"/>
-      <c r="B164" s="60"/>
-      <c r="C164" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D164">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="43"/>
-      <c r="B165" s="60"/>
-      <c r="C165" s="30">
-        <v>-0.2</v>
-      </c>
-      <c r="D165">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="43"/>
-      <c r="B166" s="60"/>
-      <c r="C166" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D166">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="43"/>
-      <c r="B167" s="60"/>
-      <c r="C167" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D167">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="43"/>
-      <c r="B168" s="60"/>
-      <c r="C168" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D168">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="43"/>
-      <c r="B169" s="60"/>
-      <c r="C169" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D169">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="43"/>
-      <c r="B170" s="60"/>
-      <c r="C170" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D170">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="43"/>
-      <c r="B171" s="60"/>
-      <c r="C171" s="30">
-        <v>-0.3</v>
-      </c>
-      <c r="D171">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="43"/>
-      <c r="B172" s="60"/>
-      <c r="C172" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D172">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="43"/>
-      <c r="B173" s="60"/>
-      <c r="C173" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D173">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="43"/>
-      <c r="B174" s="60"/>
-      <c r="C174" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D174">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="43"/>
-      <c r="B175" s="60"/>
-      <c r="C175" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D175">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="43"/>
-      <c r="B176" s="60"/>
-      <c r="C176" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D176">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.89999999999999991</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="43"/>
-      <c r="B177" s="60"/>
-      <c r="C177" s="30">
-        <v>-0.6</v>
-      </c>
-      <c r="D177">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.2999999999999998</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="43"/>
-      <c r="B178" s="60"/>
-      <c r="C178" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D178">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.7000000000000002</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="43"/>
-      <c r="B179" s="60"/>
-      <c r="C179" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D179">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="43"/>
-      <c r="B180" s="60"/>
-      <c r="C180" s="30">
-        <v>-0.5</v>
-      </c>
-      <c r="D180">
-        <f t="shared" ca="1" si="3"/>
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="43"/>
-      <c r="B181" s="60"/>
-      <c r="C181" s="30">
-        <v>-0.4</v>
-      </c>
-      <c r="D181">
-        <f t="shared" ca="1" si="3"/>
-        <v>-0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="43"/>
-      <c r="B182" s="60"/>
-      <c r="C182" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="D182">
-        <f t="shared" ref="D182:D189" ca="1" si="4">C182- RANDBETWEEN(1, 10)/10</f>
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="43"/>
-      <c r="B183" s="60"/>
-      <c r="C183" s="30">
-        <v>-0.8</v>
-      </c>
-      <c r="D183">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="43"/>
-      <c r="B184" s="60"/>
-      <c r="C184" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D184">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="43"/>
-      <c r="B185" s="60"/>
-      <c r="C185" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D185">
-        <f t="shared" ca="1" si="4"/>
-        <v>-0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="43"/>
-      <c r="B186" s="60"/>
-      <c r="C186" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D186">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="43"/>
-      <c r="B187" s="60"/>
-      <c r="C187" s="30">
-        <v>-0.1</v>
-      </c>
-      <c r="D187">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="43"/>
-      <c r="B188" s="60"/>
-      <c r="C188" s="30">
-        <v>-1</v>
-      </c>
-      <c r="D188">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="43"/>
-      <c r="B189" s="60"/>
-      <c r="C189" s="30">
-        <v>-0.9</v>
-      </c>
-      <c r="D189">
-        <f t="shared" ca="1" si="4"/>
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="43"/>
-      <c r="B190" s="60"/>
-      <c r="C190" s="30"/>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="43"/>
-      <c r="B191" s="60"/>
-      <c r="C191" s="30"/>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="43"/>
-      <c r="B192" s="60"/>
-      <c r="C192" s="30"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="43"/>
-      <c r="B193" s="60"/>
-      <c r="C193" s="30"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="43"/>
-      <c r="B194" s="60"/>
-      <c r="C194" s="30"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="43"/>
-      <c r="B195" s="60"/>
-      <c r="C195" s="30"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="43"/>
-      <c r="B196" s="60"/>
-      <c r="C196" s="30"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="43"/>
-      <c r="B197" s="60"/>
-      <c r="C197" s="30"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="43"/>
-      <c r="B198" s="60"/>
-      <c r="C198" s="30"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="43"/>
-      <c r="B199" s="60"/>
-      <c r="C199" s="30"/>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="43"/>
-      <c r="B200" s="60"/>
-      <c r="C200" s="30"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="43"/>
-      <c r="B201" s="60"/>
-      <c r="C201" s="30"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="43"/>
-      <c r="B202" s="60"/>
-      <c r="C202" s="30"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="43"/>
-      <c r="B203" s="60"/>
-      <c r="C203" s="30"/>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="43"/>
-      <c r="B204" s="60"/>
-      <c r="C204" s="30"/>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="43"/>
-      <c r="B205" s="60"/>
-      <c r="C205" s="30"/>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="43"/>
-      <c r="B206" s="60"/>
-      <c r="C206" s="30"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="43"/>
-      <c r="B207" s="60"/>
-      <c r="C207" s="30"/>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="43"/>
-      <c r="B208" s="60"/>
-      <c r="C208" s="30"/>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="43"/>
-      <c r="B209" s="60"/>
-      <c r="C209" s="30"/>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" s="43"/>
-      <c r="B210" s="60"/>
-      <c r="C210" s="30"/>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" s="43"/>
-      <c r="B211" s="60"/>
-      <c r="C211" s="30"/>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" s="43"/>
-      <c r="B212" s="60"/>
-      <c r="C212" s="30"/>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" s="43"/>
-      <c r="B213" s="60"/>
-      <c r="C213" s="30"/>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" s="43"/>
-      <c r="B214" s="60"/>
-      <c r="C214" s="30"/>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" s="43"/>
-      <c r="B215" s="60"/>
-      <c r="C215" s="30"/>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" s="43"/>
-      <c r="B216" s="60"/>
-      <c r="C216" s="30"/>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" s="43"/>
-      <c r="B217" s="60"/>
-      <c r="C217" s="30"/>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" s="43"/>
-      <c r="B218" s="60"/>
-      <c r="C218" s="30"/>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" s="43"/>
-      <c r="B219" s="60"/>
-      <c r="C219" s="30"/>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" s="43"/>
-      <c r="B220" s="60"/>
-      <c r="C220" s="30"/>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" s="43"/>
-      <c r="B221" s="60"/>
-      <c r="C221" s="30"/>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" s="43"/>
-      <c r="B222" s="60"/>
-      <c r="C222" s="30"/>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" s="43"/>
-      <c r="B223" s="60"/>
-      <c r="C223" s="30"/>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" s="43"/>
-      <c r="B224" s="60"/>
-      <c r="C224" s="30"/>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A225" s="43"/>
-      <c r="B225" s="60"/>
-      <c r="C225" s="30"/>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A226" s="43"/>
-      <c r="B226" s="60"/>
-      <c r="C226" s="30"/>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A227" s="43"/>
-      <c r="B227" s="60"/>
-      <c r="C227" s="30"/>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A228" s="43"/>
-      <c r="B228" s="60"/>
-      <c r="C228" s="30"/>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A229" s="43"/>
-      <c r="B229" s="60"/>
-      <c r="C229" s="30"/>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A230" s="43"/>
-      <c r="B230" s="60"/>
-      <c r="C230" s="30"/>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A231" s="43"/>
-      <c r="B231" s="60"/>
-      <c r="C231" s="30"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -6944,11 +5192,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -7089,11 +5337,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -7166,11 +5414,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -7311,11 +5559,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -7726,11 +5974,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
